--- a/data/Distribution.xlsx
+++ b/data/Distribution.xlsx
@@ -6,7 +6,7 @@
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$C$69</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$F$89</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -15,15 +15,73 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={1aa5b0d0-9f3a-4844-8a03-ad13215feec9}</author>
-    <author>tc={5fb511cc-cee9-4f48-b86c-c70ce54b2f2e}</author>
-    <author>tc={8bf2ece6-fde9-4a25-b22d-5038092e0fa5}</author>
-    <author>tc={8e5894e3-2e56-4408-bafb-1eefeb7800f6}</author>
-    <author>tc={dfcda80b-bb1a-4654-896e-e80146cbdc25}</author>
-    <author>tc={f257df23-8bea-47f7-874f-7456d076760b}</author>
+    <author>tc={140aeef9-3785-4e14-901f-ab744247e5bb}</author>
+    <author>tc={179780df-62e3-460b-b364-b5ebf646a28a}</author>
+    <author>tc={1ff66cbb-6d6b-4c9a-832b-0a29c3c3cfd7}</author>
+    <author>tc={877857ef-abbc-41db-bba3-2cd537ae6c71}</author>
+    <author>tc={8abf23c8-06a0-4d1e-861b-87295a9c5d03}</author>
+    <author>tc={9f4b347a-3005-46a5-a27e-c30d8f5648a2}</author>
+    <author>tc={da2fd15d-2be4-4a60-9277-cab16e8ac364}</author>
+    <author>tc={e2bbbd25-7f54-4f59-94e5-ad4090a6edd2}</author>
+    <author>tc={f851d448-3826-4dc4-bdeb-ac04a0b27433}</author>
+    <author>tc={fc36dcdc-27c0-4cf9-9f92-bd1b0106c9cc}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{1aa5b0d0-9f3a-4844-8a03-ad13215feec9}" ref="A1">
+    <comment authorId="0" xr:uid="{140aeef9-3785-4e14-901f-ab744247e5bb}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Cornus alba
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{179780df-62e3-460b-b364-b5ebf646a28a}" ref="A72">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Not in the book flora of the chicago region but says native on morton website
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{1ff66cbb-6d6b-4c9a-832b-0a29c3c3cfd7}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Same as amurensis var. amurensis
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{877857ef-abbc-41db-bba3-2cd537ae6c71}" ref="A83">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Cornus schindleri subsp. poliophylla
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{8abf23c8-06a0-4d1e-861b-87295a9c5d03}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Synonym of Acer platanoides subsp. turkestanicum
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{9f4b347a-3005-46a5-a27e-c30d8f5648a2}" ref="A1">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Cornus walteri Wangerin
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{da2fd15d-2be4-4a60-9277-cab16e8ac364}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,25 +90,25 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{5fb511cc-cee9-4f48-b86c-c70ce54b2f2e}" ref="A1">
+    <comment authorId="7" xr:uid="{e2bbbd25-7f54-4f59-94e5-ad4090a6edd2}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Synonym of Acer platanoides subsp. turkestanicum
+	Says its synonym of Parthenocissus tricuspidata
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{8bf2ece6-fde9-4a25-b22d-5038092e0fa5}" ref="A1">
+    <comment authorId="8" xr:uid="{f851d448-3826-4dc4-bdeb-ac04a0b27433}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	Same as amurensis var. amurensis
+	Acer tataricum subsp ginnala
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{8e5894e3-2e56-4408-bafb-1eefeb7800f6}" ref="A1">
+    <comment authorId="9" xr:uid="{fc36dcdc-27c0-4cf9-9f92-bd1b0106c9cc}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -59,30 +117,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{dfcda80b-bb1a-4654-896e-e80146cbdc25}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Acer tataricum subsp ginnala
-</t>
-      </text>
-    </comment>
-    <comment authorId="5" xr:uid="{f257df23-8bea-47f7-874f-7456d076760b}" ref="A1">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Says its synonym of Parthenocissus tricuspidata
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="97">
   <si>
     <t>SP Cleaned</t>
   </si>
@@ -90,7 +130,16 @@
     <t>Chicago Native</t>
   </si>
   <si>
-    <t>Countinent of origin</t>
+    <t>EU</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>AF</t>
   </si>
   <si>
     <t>Tilia</t>
@@ -114,7 +163,7 @@
     <t>F</t>
   </si>
   <si>
-    <t>AS</t>
+    <t>T</t>
   </si>
   <si>
     <t>Tilia chinensis</t>
@@ -123,15 +172,9 @@
     <t>Tilia cordata</t>
   </si>
   <si>
-    <t>EU</t>
-  </si>
-  <si>
     <t>Tilia dasystyla</t>
   </si>
   <si>
-    <t>EU AS</t>
-  </si>
-  <si>
     <t>Tilia henryana</t>
   </si>
   <si>
@@ -159,12 +202,6 @@
     <t>Tilia americana</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Cercis canadensis</t>
   </si>
   <si>
@@ -198,9 +235,6 @@
     <t>Acer campestre</t>
   </si>
   <si>
-    <t>EU AS AF</t>
-  </si>
-  <si>
     <t>Acer cappadocicum</t>
   </si>
   <si>
@@ -319,6 +353,66 @@
   </si>
   <si>
     <t>Acer tschonoskii</t>
+  </si>
+  <si>
+    <t>Cornus alba</t>
+  </si>
+  <si>
+    <t>Cornus alternifolia</t>
+  </si>
+  <si>
+    <t>Cornus amomum</t>
+  </si>
+  <si>
+    <t>Cornus bretschneideri</t>
+  </si>
+  <si>
+    <t>Cornus controversa</t>
+  </si>
+  <si>
+    <t>Cornus darvasica</t>
+  </si>
+  <si>
+    <t>Cornus drummondii</t>
+  </si>
+  <si>
+    <t>Cornus florida</t>
+  </si>
+  <si>
+    <t>Cornus foemina</t>
+  </si>
+  <si>
+    <t>Cornus kousa</t>
+  </si>
+  <si>
+    <t>Cornus macrophylla</t>
+  </si>
+  <si>
+    <t>Cornus mas L.</t>
+  </si>
+  <si>
+    <t>Cornus officinalis</t>
+  </si>
+  <si>
+    <t>Cornus poliophylla C.K.Schneid. &amp; Wangerin</t>
+  </si>
+  <si>
+    <t>Cornus quinquenervis</t>
+  </si>
+  <si>
+    <t>Cornus racemosa</t>
+  </si>
+  <si>
+    <t>Cornus rugosa</t>
+  </si>
+  <si>
+    <t>Cornus sanguinea</t>
+  </si>
+  <si>
+    <t>Cornus sericea</t>
+  </si>
+  <si>
+    <t>Cornus walteri Wangerin</t>
   </si>
 </sst>
 </file>
@@ -389,7 +483,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Miriam Hafkin" id="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" providerId="google-sheets"/>
+  <x18tc:person displayName="Miriam Hafkin" id="{06048b11-ab43-471f-846c-3a7790fa356f}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -589,22 +683,34 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:58:49.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{f257df23-8bea-47f7-874f-7456d076760b}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-10T17:02:44.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{140aeef9-3785-4e14-901f-ab744247e5bb}" done="0">
+    <x18tc:text xml:space="preserve">Cornus alba</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:58:49.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{e2bbbd25-7f54-4f59-94e5-ad4090a6edd2}" done="0">
     <x18tc:text xml:space="preserve">Says its synonym of Parthenocissus tricuspidata</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T17:07:34.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{5fb511cc-cee9-4f48-b86c-c70ce54b2f2e}" done="0">
+  <x18tc:threadedComment ref="A83" dT="2026-07-10T17:02:08.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{877857ef-abbc-41db-bba3-2cd537ae6c71}" done="1">
+    <x18tc:text xml:space="preserve">Cornus schindleri subsp. poliophylla</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T17:07:34.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{8abf23c8-06a0-4d1e-861b-87295a9c5d03}" done="0">
     <x18tc:text xml:space="preserve">Synonym of Acer platanoides subsp. turkestanicum</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:57:34.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{1aa5b0d0-9f3a-4844-8a03-ad13215feec9}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:57:34.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{da2fd15d-2be4-4a60-9277-cab16e8ac364}" done="0">
     <x18tc:text xml:space="preserve">This name is a synonym of Acer saccharum subsp. nigrum (F.Michx.) Desmarais by Sapindaceae.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:28:53.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{8bf2ece6-fde9-4a25-b22d-5038092e0fa5}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:28:53.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{1ff66cbb-6d6b-4c9a-832b-0a29c3c3cfd7}" done="0">
     <x18tc:text xml:space="preserve">Same as amurensis var. amurensis</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:52:12.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{8e5894e3-2e56-4408-bafb-1eefeb7800f6}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-10T16:56:23.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{9f4b347a-3005-46a5-a27e-c30d8f5648a2}" done="0">
+    <x18tc:text xml:space="preserve">Cornus walteri Wangerin</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A72" dT="2026-07-10T17:12:32.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{179780df-62e3-460b-b364-b5ebf646a28a}" done="1">
+    <x18tc:text xml:space="preserve">Not in the book flora of the chicago region but says native on morton website</x18tc:text>
+  </x18tc:threadedComment>
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:52:12.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{fc36dcdc-27c0-4cf9-9f92-bd1b0106c9cc}" done="0">
     <x18tc:text xml:space="preserve">Says its a synonym of Acer pictum subsp. mono</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:56:40.00" personId="{a9669ae7-7ec2-4dac-9573-da5009d9a925}" id="{dfcda80b-bb1a-4654-896e-e80146cbdc25}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-07-08T16:56:40.00" personId="{06048b11-ab43-471f-846c-3a7790fa356f}" id="{f851d448-3826-4dc4-bdeb-ac04a0b27433}" done="0">
     <x18tc:text xml:space="preserve">Acer tataricum subsp ginnala</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -618,7 +724,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="24.5"/>
-    <col customWidth="1" min="3" max="3" width="25.88"/>
+    <col customWidth="1" min="3" max="6" width="25.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,760 +734,1781 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>10</v>
+      <c r="B71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$C$69"/>
+  <autoFilter ref="$A$1:$F$89"/>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
 </worksheet>
